--- a/_ForDRA/BVSimulationFiles/90.xlsx
+++ b/_ForDRA/BVSimulationFiles/90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00050390625</v>
+        <v>0.010078125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000518905691501465</v>
+        <v>0.0103781138300293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005337916159955035</v>
+        <v>0.01067583231991007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000548564642822741</v>
+        <v>0.01097129285645482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005632253883484896</v>
+        <v>0.01126450776696979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005777744659760985</v>
+        <v>0.01155548931952197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005922124861602463</v>
+        <v>0.01184424972320493</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006065400564201775</v>
+        <v>0.01213080112840355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00062075778135288</v>
+        <v>0.0124151556270576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006348662626462087</v>
+        <v>0.01269732525292417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006488660990919507</v>
+        <v>0.01297732198183901</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006627578865988328</v>
+        <v>0.01325515773197666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006765422182054782</v>
+        <v>0.01353084436410956</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0006902196840933018</v>
+        <v>0.01380439368186604</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007037908715993534</v>
+        <v>0.01407581743198707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007172563652291042</v>
+        <v>0.01434512730458208</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007306167466691788</v>
+        <v>0.01461233493338358</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007438725948000326</v>
+        <v>0.01487745189600065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000757024485708573</v>
+        <v>0.01514048971417146</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007700729927007298</v>
+        <v>0.0154014598540146</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00050390625</v>
+        <v>0.010078125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000518905691501465</v>
+        <v>0.0103781138300293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005337916159955035</v>
+        <v>0.01067583231991007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000548564642822741</v>
+        <v>0.01097129285645482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005632253883484896</v>
+        <v>0.01126450776696979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005777744659760985</v>
+        <v>0.01155548931952197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005922124861602463</v>
+        <v>0.01184424972320493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006065400564201775</v>
+        <v>0.01213080112840355</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00062075778135288</v>
+        <v>0.0124151556270576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006348662626462087</v>
+        <v>0.01269732525292417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006488660990919507</v>
+        <v>0.01297732198183901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006627578865988328</v>
+        <v>0.01325515773197666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006765422182054782</v>
+        <v>0.01353084436410956</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006902196840933018</v>
+        <v>0.01380439368186604</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007037908715993534</v>
+        <v>0.01407581743198707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007172563652291042</v>
+        <v>0.01434512730458208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007306167466691788</v>
+        <v>0.01461233493338358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007438725948000326</v>
+        <v>0.01487745189600065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000757024485708573</v>
+        <v>0.01514048971417146</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007700729927007298</v>
+        <v>0.0154014598540146</v>
       </c>
     </row>
   </sheetData>
